--- a/INSTANCES/instances_xlsx/A_MTN_1/57FL_2A_7.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_1/57FL_2A_7.xlsx
@@ -2565,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
